--- a/public/datos/3.2_Conteo_condicional.xlsx
+++ b/public/datos/3.2_Conteo_condicional.xlsx
@@ -7,8 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Documentos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Indicadores_Proceso" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Enunciado_Caso" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Base_Documentos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Tablero_Eficiencia" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,6 +427,168 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Sección</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Detalle del Requerimiento / Parámetros del Caso</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Código de Actividad</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Título del Caso</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Métricas de rendimiento procesal y estadísticas condicionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Organización</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Lácteos del Caribe S.A.S. - Sistema Integrado de Gestión</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1. Situación Problema</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>El SIG evalúa la eficiencia de los procesos de Lácteos del Caribe midiendo la tasa de vigencia documental y los tiempos de revisión técnica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2. Misión del Aprendiz</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Construir el tablero de métricas por proceso usando CONTAR.SI, CONTAR.SI.CONJUNTO y PROMEDIO.SI, protegiendo las fórmulas contra divisiones por cero con SI.ERROR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Requerimiento 1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Total Documentos: =CONTAR.SI() en Base_Documentos por proceso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Requerimiento 2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Documentos Vigentes: =CONTAR.SI.CONJUNTO() por proceso y estado 'Vigente'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Requerimiento 3</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>% Cobertura Vigente: Vigentes / Total formateado en porcentaje con un decimal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Requerimiento 4</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Promedio Días Revisión: =PROMEDIO.SI() por proceso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Requerimiento 5</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Blindaje contra Errores: PA-05 Gestión Ambiental no tiene documentos (0/0 genera #¡DIV/0!). Aplica =SI.ERROR(Vigentes/Total; 0) y =SI.ERROR(PROMEDIO.SI(...); 0).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Dificultad Clave / Regla Técnica</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Un informe directivo no puede contener errores #¡DIV/0!. El uso de SI.ERROR es obligatorio para aprobar la auditoría de la hoja.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1262,52 +1425,63 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Código</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Proceso</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Total documentos</t>
-        </is>
-      </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Vigentes</t>
+          <t>Total Documentos (=CONTAR.SI)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>% Vigentes</t>
+          <t>Vigentes (=CONTAR.SI.CONJUNTO)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Promedio días de revisión</t>
+          <t>% Cobertura Vigente</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Promedio Días Revisión (=PROMEDIO.SI)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>PE-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>Direccionamiento estratégico</t>
         </is>
       </c>
@@ -1315,6 +1489,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>PE-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>Gestión de la calidad</t>
         </is>
       </c>
@@ -1322,6 +1501,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>PM-01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Producción</t>
         </is>
       </c>
@@ -1329,6 +1513,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>PM-02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>Comercial y ventas</t>
         </is>
       </c>
@@ -1336,6 +1525,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>PM-03</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>Logística y distribución</t>
         </is>
       </c>
@@ -1343,6 +1537,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>PA-01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>Talento humano</t>
         </is>
       </c>
@@ -1350,6 +1549,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>PA-02</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>Compras</t>
         </is>
       </c>
@@ -1357,6 +1561,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>PA-03</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>Mantenimiento</t>
         </is>
       </c>
@@ -1364,12 +1573,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>PA-04</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>Seguridad y salud en el trabajo</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
+        <is>
+          <t>PA-05</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>Gestión ambiental</t>
         </is>
